--- a/daehwan/HGU PPS Camp 문제목록.xlsx
+++ b/daehwan/HGU PPS Camp 문제목록.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8c01d0c1ce5aee91/Desktop/python/PPS---CodingCamp/daehwan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="11_8CC9AD31FD3A506B96111A20541687E23802AF23" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0028A01D-0109-461D-B879-84906C715631}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="11_8CC9AD31FD3A506B96111A20541687E23802AF23" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BC642AE-685E-4902-8E09-16F35031DAE7}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="780" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="문제목록" sheetId="1" r:id="rId1"/>
